--- a/excel/finanzas-master.xlsx
+++ b/excel/finanzas-master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\japaricio\Dropbox\Cuentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319137BD-64B9-4EE4-B38A-01684D6B0BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB4BEE5-2C7F-413D-A401-3D4B7328D9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MASTER" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DESPIDO!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MASTER!$A$1:$K$1</definedName>
   </definedNames>
-  <calcPr calcId="191028" concurrentCalc="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -367,7 +367,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="132">
   <si>
     <t>id</t>
   </si>
@@ -760,6 +760,9 @@
   </si>
   <si>
     <t>semanal</t>
+  </si>
+  <si>
+    <t>Cloud Apple</t>
   </si>
 </sst>
 </file>
@@ -1555,7 +1558,7 @@
         <v>41</v>
       </c>
       <c r="E10" s="5">
-        <v>1350</v>
+        <v>1414</v>
       </c>
       <c r="F10" s="15">
         <v>2026</v>
@@ -2092,7 +2095,7 @@
         <v>29</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="E28" s="7">
         <v>1</v>
@@ -3044,7 +3047,7 @@
       </c>
       <c r="E10" s="5">
         <f>MASTER!E10-MASTER!E10*$L$9</f>
-        <v>810</v>
+        <v>848.4</v>
       </c>
       <c r="F10" s="15">
         <v>2026</v>
@@ -3595,7 +3598,7 @@
         <v>29</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="E28" s="5">
         <f>MASTER!E28-MASTER!E28*$L$9</f>
@@ -4324,7 +4327,7 @@
     <mergeCell ref="A9:K9"/>
     <mergeCell ref="A47:K47"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2:K2 A3 A4:K8 A9 A47 A48:K509 A10:K46">
+  <conditionalFormatting sqref="A2:K2 A3 A4:K8 A9 A10:K46 A47 A48:K509">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND($A2&lt;&gt;"",$B2&lt;&gt;"",$J2=0)</formula>
     </cfRule>

--- a/excel/finanzas-master.xlsx
+++ b/excel/finanzas-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\japaricio\Dropbox\Cuentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB4BEE5-2C7F-413D-A401-3D4B7328D9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CAB6F2A-78EA-4F14-9567-9A6CC90E21E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1558,7 +1558,7 @@
         <v>41</v>
       </c>
       <c r="E10" s="5">
-        <v>1414</v>
+        <v>1380</v>
       </c>
       <c r="F10" s="15">
         <v>2026</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="E10" s="5">
         <f>MASTER!E10-MASTER!E10*$L$9</f>
-        <v>848.4</v>
+        <v>828</v>
       </c>
       <c r="F10" s="15">
         <v>2026</v>

--- a/excel/finanzas-master.xlsx
+++ b/excel/finanzas-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\japaricio\Dropbox\Cuentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CAB6F2A-78EA-4F14-9567-9A6CC90E21E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46717F7B-9581-47F0-AFB7-83F7D89EA366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1558,7 +1558,7 @@
         <v>41</v>
       </c>
       <c r="E10" s="5">
-        <v>1380</v>
+        <v>1385</v>
       </c>
       <c r="F10" s="15">
         <v>2026</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="E10" s="5">
         <f>MASTER!E10-MASTER!E10*$L$9</f>
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="F10" s="15">
         <v>2026</v>

--- a/excel/finanzas-master.xlsx
+++ b/excel/finanzas-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\japaricio\Dropbox\Cuentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46717F7B-9581-47F0-AFB7-83F7D89EA366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDC82CB-376F-412B-8B7B-0F9BECE6F529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1558,7 +1558,7 @@
         <v>41</v>
       </c>
       <c r="E10" s="5">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="F10" s="15">
         <v>2026</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="E10" s="5">
         <f>MASTER!E10-MASTER!E10*$L$9</f>
-        <v>831</v>
+        <v>831.6</v>
       </c>
       <c r="F10" s="15">
         <v>2026</v>
